--- a/qUERY EXPLANATION.xlsx
+++ b/qUERY EXPLANATION.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abinaya\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A46EBA3-3145-429F-B316-124EF8BAEEE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F210F58-54C5-4C77-8688-D0044DC33FED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{761FCC1B-5A29-4159-8730-9EEFF73DF7B3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{761FCC1B-5A29-4159-8730-9EEFF73DF7B3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="32">
   <si>
     <t>Field</t>
   </si>
@@ -193,6 +195,216 @@
   </si>
   <si>
     <t>Lead No, Conditions for Approval, Document Name, Remarks</t>
+  </si>
+  <si>
+    <t>1. User Access Report – Home Finance LMS</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Tables</t>
+  </si>
+  <si>
+    <r>
+      <t>FRM_MENU</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>FRM_USERROLE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>FRM_USER</t>
+    </r>
+  </si>
+  <si>
+    <t>Joins</t>
+  </si>
+  <si>
+    <t>FRM_MENU.Menu_Role = FRM_USERROLE.USER_ROLEFRM_USER.LoginID = FRM_USERROLE.USER_USERID</t>
+  </si>
+  <si>
+    <t>Fields Required</t>
+  </si>
+  <si>
+    <t>Staff Name, Staff No., Department, User Name/Login ID, Last Login Date, User Status, System Name, Menu/Privilege Name, User Role</t>
+  </si>
+  <si>
+    <t>Additional Requirement</t>
+  </si>
+  <si>
+    <t>Include financial limit details, wherever a financial limit is assigned to the user</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Menu/Privilege Name contains </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Report"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Menu Status = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A (Active)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">User Role Status = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A (Active)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">User Status = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A (Active)</t>
+    </r>
+  </si>
+  <si>
+    <t>2. User Role / Group Privileges – Home Finance LMS</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Menu Status = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A (Active)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">User Role Status = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A (Active)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">User Status = </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A (Active)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -263,7 +475,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -279,6 +491,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -729,4 +953,123 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42A18D63-9798-4422-A97D-9582E1D3D2F9}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="91.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="195" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="285" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="165" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="270" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E4796D0-086B-404F-8685-C9917885A810}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="91.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="195" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="285" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="195" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/qUERY EXPLANATION.xlsx
+++ b/qUERY EXPLANATION.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abinaya\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F210F58-54C5-4C77-8688-D0044DC33FED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73799961-77D4-42CF-8E97-847198EA3F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{761FCC1B-5A29-4159-8730-9EEFF73DF7B3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{761FCC1B-5A29-4159-8730-9EEFF73DF7B3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="42">
   <si>
     <t>Field</t>
   </si>
@@ -405,6 +406,147 @@
       </rPr>
       <t>A (Active)</t>
     </r>
+  </si>
+  <si>
+    <t>Dear Dilshad,</t>
+  </si>
+  <si>
+    <t>As discussed, the process is as follows:</t>
+  </si>
+  <si>
+    <t>1. The user first pulls the AECB details.</t>
+  </si>
+  <si>
+    <t>2. The Initiate Policy Engine service is then called.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. For the case you mentioned, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AECB_Over_due_Emi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AECB_Over_Due_CC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> are blank.</t>
+    </r>
+  </si>
+  <si>
+    <t>4. Since no records were found for these details, the AECB service is triggered and returns a blank response in the response XML.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">5. Subsequently, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AECB_Over_due_Emi</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AECB_Over_Due_CC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> are passed as blank to the Policy Engine service.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">6. Passing the fields as empty when the corresponding AECB data is not available is the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>existing/current system behavior</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Thanks,</t>
+  </si>
+  <si>
+    <t>Hariprasath</t>
   </si>
 </sst>
 </file>
@@ -475,7 +617,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -503,6 +645,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1072,4 +1217,82 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AC8C148-D073-4F9E-88EA-1A6E5D29186B}">
+  <dimension ref="A1:A18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10"/>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10"/>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="10"/>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10"/>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="10"/>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="10"/>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/qUERY EXPLANATION.xlsx
+++ b/qUERY EXPLANATION.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abinaya\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FAB97108-73DD-4372-ABB9-DF458FF52911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A771B2B5-4148-4884-ABB2-830E55F0DA61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{DE50BC6D-62B4-4FC4-8766-6D8EDCEB67E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{DE50BC6D-62B4-4FC4-8766-6D8EDCEB67E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="56">
   <si>
     <t>Service</t>
   </si>
@@ -178,6 +179,36 @@
   </si>
   <si>
     <t>—</t>
+  </si>
+  <si>
+    <t>Activity</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>REST API contract analysis &amp; SOA-to-REST mapping</t>
+  </si>
+  <si>
+    <t>Common REST client/framework changes</t>
+  </si>
+  <si>
+    <t>Authentication/security/header handling</t>
+  </si>
+  <si>
+    <t>Error handling/logging/retry changes</t>
+  </si>
+  <si>
+    <t>SIT/UAT coordination &amp; defect fixing</t>
+  </si>
+  <si>
+    <t>Deployment/cutover/rollback support</t>
+  </si>
+  <si>
+    <t>Documentation / KT</t>
+  </si>
+  <si>
+    <t>Common effort</t>
   </si>
 </sst>
 </file>
@@ -251,8 +282,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -280,6 +323,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -618,448 +664,448 @@
   <dimension ref="A1:I15"/>
   <sheetFormatPr defaultColWidth="53.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="5.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="50.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="53.5703125" style="5"/>
+    <col min="1" max="1" width="18" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.85546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="5.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="50.5703125" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="53.5703125" style="9"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="4" t="s">
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="11">
         <v>3</v>
       </c>
-      <c r="D2" s="7">
-        <v>1</v>
-      </c>
-      <c r="E2" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="F2" s="7">
+      <c r="D2" s="11">
+        <v>1</v>
+      </c>
+      <c r="E2" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="F2" s="11">
         <v>1.5</v>
       </c>
-      <c r="G2" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="H2" s="4">
+      <c r="G2" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="H2" s="8">
         <v>6.5</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="11">
         <v>3</v>
       </c>
-      <c r="D3" s="7">
-        <v>1</v>
-      </c>
-      <c r="E3" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="F3" s="7">
+      <c r="D3" s="11">
+        <v>1</v>
+      </c>
+      <c r="E3" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="F3" s="11">
         <v>1.5</v>
       </c>
-      <c r="G3" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="H3" s="4">
+      <c r="G3" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="H3" s="8">
         <v>6.5</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="10" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="11">
         <v>3</v>
       </c>
-      <c r="D4" s="7">
-        <v>1</v>
-      </c>
-      <c r="E4" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="F4" s="7">
+      <c r="D4" s="11">
+        <v>1</v>
+      </c>
+      <c r="E4" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="F4" s="11">
         <v>1.5</v>
       </c>
-      <c r="G4" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="H4" s="4">
+      <c r="G4" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="H4" s="8">
         <v>6.5</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="10" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="11">
         <v>3</v>
       </c>
-      <c r="D5" s="7">
-        <v>1</v>
-      </c>
-      <c r="E5" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="F5" s="7">
+      <c r="D5" s="11">
+        <v>1</v>
+      </c>
+      <c r="E5" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="F5" s="11">
         <v>1.5</v>
       </c>
-      <c r="G5" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="H5" s="4">
+      <c r="G5" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="H5" s="8">
         <v>6.5</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="10" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="11">
         <v>4</v>
       </c>
-      <c r="D6" s="7">
-        <v>1</v>
-      </c>
-      <c r="E6" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="F6" s="7">
-        <v>2</v>
-      </c>
-      <c r="G6" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="H6" s="4">
+      <c r="D6" s="11">
+        <v>1</v>
+      </c>
+      <c r="E6" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="F6" s="11">
+        <v>2</v>
+      </c>
+      <c r="G6" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="H6" s="8">
         <v>8</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="10" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="11">
         <v>4</v>
       </c>
-      <c r="D7" s="7">
-        <v>1</v>
-      </c>
-      <c r="E7" s="7">
-        <v>1</v>
-      </c>
-      <c r="F7" s="7">
-        <v>2</v>
-      </c>
-      <c r="G7" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="H7" s="4">
+      <c r="D7" s="11">
+        <v>1</v>
+      </c>
+      <c r="E7" s="11">
+        <v>1</v>
+      </c>
+      <c r="F7" s="11">
+        <v>2</v>
+      </c>
+      <c r="G7" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="H7" s="8">
         <v>8.5</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="10" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="11">
         <v>3</v>
       </c>
-      <c r="D8" s="7">
-        <v>1</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="F8" s="7">
+      <c r="D8" s="11">
+        <v>1</v>
+      </c>
+      <c r="E8" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="F8" s="11">
         <v>1.5</v>
       </c>
-      <c r="G8" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="H8" s="4">
+      <c r="G8" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="H8" s="8">
         <v>6.5</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="11">
         <v>3</v>
       </c>
-      <c r="D9" s="7">
-        <v>1</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="F9" s="7">
+      <c r="D9" s="11">
+        <v>1</v>
+      </c>
+      <c r="E9" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="F9" s="11">
         <v>1.5</v>
       </c>
-      <c r="G9" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="H9" s="4">
+      <c r="G9" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="H9" s="8">
         <v>6.5</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="11">
         <v>3</v>
       </c>
-      <c r="D10" s="7">
-        <v>1</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="F10" s="7">
+      <c r="D10" s="11">
+        <v>1</v>
+      </c>
+      <c r="E10" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="F10" s="11">
         <v>1.5</v>
       </c>
-      <c r="G10" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="H10" s="4">
+      <c r="G10" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="H10" s="8">
         <v>6.5</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="10" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="11">
         <v>3</v>
       </c>
-      <c r="D11" s="7">
-        <v>1</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="F11" s="7">
+      <c r="D11" s="11">
+        <v>1</v>
+      </c>
+      <c r="E11" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="11">
         <v>1.5</v>
       </c>
-      <c r="G11" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="H11" s="4">
+      <c r="G11" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="H11" s="8">
         <v>6.5</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="10" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="11">
         <v>3</v>
       </c>
-      <c r="D12" s="7">
-        <v>1</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="F12" s="7">
+      <c r="D12" s="11">
+        <v>1</v>
+      </c>
+      <c r="E12" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="F12" s="11">
         <v>1.5</v>
       </c>
-      <c r="G12" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="H12" s="4">
+      <c r="G12" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="H12" s="8">
         <v>6.5</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="10" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="11">
         <v>3</v>
       </c>
-      <c r="D13" s="7">
-        <v>1</v>
-      </c>
-      <c r="E13" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="F13" s="7">
+      <c r="D13" s="11">
+        <v>1</v>
+      </c>
+      <c r="E13" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="F13" s="11">
         <v>1.5</v>
       </c>
-      <c r="G13" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="H13" s="4">
+      <c r="G13" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="H13" s="8">
         <v>6.5</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="10" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="11">
         <v>3</v>
       </c>
-      <c r="D14" s="7">
-        <v>1</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="F14" s="7">
+      <c r="D14" s="11">
+        <v>1</v>
+      </c>
+      <c r="E14" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="F14" s="11">
         <v>1.5</v>
       </c>
-      <c r="G14" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="H14" s="4">
+      <c r="G14" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="H14" s="8">
         <v>6.5</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="I14" s="10" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="11">
         <v>4</v>
       </c>
-      <c r="D15" s="7">
-        <v>1</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="F15" s="7">
-        <v>2</v>
-      </c>
-      <c r="G15" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="H15" s="4">
+      <c r="D15" s="11">
+        <v>1</v>
+      </c>
+      <c r="E15" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="F15" s="11">
+        <v>2</v>
+      </c>
+      <c r="G15" s="11">
+        <v>0.5</v>
+      </c>
+      <c r="H15" s="8">
         <v>8</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="I15" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1080,87 +1126,304 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="14" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+      <c r="A2" s="5">
         <v>6314</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="12" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+      <c r="A3" s="5">
         <v>3042</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="12" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+      <c r="A4" s="5">
         <v>6312</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="12" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+      <c r="A5" s="5">
         <v>3079</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="12" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
+      <c r="A6" s="5">
         <v>3080</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="6" t="s">
         <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70BA0DE1-9550-4697-A7C6-B9A09B6B282A}">
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="90" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="2">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="2">
+        <v>6</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="2">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G4" s="3">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="2">
+        <v>3</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E5" s="2">
+        <v>2</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G5" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="2">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2">
+        <v>2</v>
+      </c>
+      <c r="G6" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="75" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="2">
+        <v>2</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="2">
+        <v>2</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G8" s="3">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="3">
+        <v>27</v>
+      </c>
+      <c r="C9" s="3">
+        <v>16</v>
+      </c>
+      <c r="D9" s="3">
+        <v>8.5</v>
+      </c>
+      <c r="E9" s="3">
+        <v>14</v>
+      </c>
+      <c r="F9" s="3">
+        <v>6.5</v>
+      </c>
+      <c r="G9" s="3">
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/qUERY EXPLANATION.xlsx
+++ b/qUERY EXPLANATION.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abinaya\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A771B2B5-4148-4884-ABB2-830E55F0DA61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5504726A-09E6-42A9-890A-DA604032E02A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{DE50BC6D-62B4-4FC4-8766-6D8EDCEB67E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{DE50BC6D-62B4-4FC4-8766-6D8EDCEB67E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="65">
   <si>
     <t>Service</t>
   </si>
@@ -209,6 +210,33 @@
   </si>
   <si>
     <t>Common effort</t>
+  </si>
+  <si>
+    <t>Primary Dev</t>
+  </si>
+  <si>
+    <t>Reuse Dev</t>
+  </si>
+  <si>
+    <t>Total Dev</t>
+  </si>
+  <si>
+    <t>QA Testing</t>
+  </si>
+  <si>
+    <t>4 × 1 = 4</t>
+  </si>
+  <si>
+    <t>1 × 1 = 1</t>
+  </si>
+  <si>
+    <t>Vymo Comments List</t>
+  </si>
+  <si>
+    <t>24 MD</t>
+  </si>
+  <si>
+    <t>44.5 MD</t>
   </si>
 </sst>
 </file>
@@ -1428,5 +1456,238 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E24F31D8-677B-4369-A864-1F59FEDAB65A}">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="15">
+        <v>6314</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" s="3">
+        <v>7</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="H2" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="I2" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J2" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="15">
+        <v>3042</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="2">
+        <v>3</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3" s="3">
+        <v>3</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J3" s="3">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="15">
+        <v>6312</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="2">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="3">
+        <v>4</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J4" s="3">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="15">
+        <v>3079</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="2">
+        <v>3</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="3">
+        <v>7</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="H5" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J5" s="3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="15">
+        <v>3080</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="3">
+        <v>3</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J6" s="3">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="B7" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="3">
+        <v>15</v>
+      </c>
+      <c r="D7" s="3">
+        <v>9</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" s="3">
+        <v>6</v>
+      </c>
+      <c r="G7" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="H7" s="3">
+        <v>9.5</v>
+      </c>
+      <c r="I7" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>